--- a/lab-standards/REHAB-lab-standard.xlsx
+++ b/lab-standards/REHAB-lab-standard.xlsx
@@ -559,6 +559,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -573,6 +577,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -642,7 +650,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -664,7 +674,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -686,7 +698,9 @@
       <c r="C18" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -708,7 +722,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>8</v>
       </c>
@@ -730,7 +746,9 @@
       <c r="C20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -752,7 +770,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -774,7 +794,9 @@
       <c r="C22" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -796,7 +818,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -818,7 +842,9 @@
       <c r="C24" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -840,7 +866,9 @@
       <c r="C25" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -862,7 +890,9 @@
       <c r="C26" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>8</v>
       </c>
@@ -884,7 +914,9 @@
       <c r="C27" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>6</v>
       </c>
@@ -906,7 +938,9 @@
       <c r="C28" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>6</v>
       </c>
@@ -928,7 +962,9 @@
       <c r="C29" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>6</v>
       </c>
@@ -950,7 +986,9 @@
       <c r="C30" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>6</v>
       </c>
@@ -972,7 +1010,9 @@
       <c r="C31" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>7</v>
       </c>
@@ -994,7 +1034,9 @@
       <c r="C32" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>7</v>
       </c>
@@ -1016,7 +1058,9 @@
       <c r="C33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>5</v>
       </c>
@@ -1038,7 +1082,9 @@
       <c r="C34" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>7</v>
       </c>
@@ -1060,7 +1106,9 @@
       <c r="C35" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>7</v>
       </c>
@@ -1082,7 +1130,9 @@
       <c r="C36" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>5</v>
       </c>
@@ -1104,7 +1154,9 @@
       <c r="C37" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>6</v>
       </c>
@@ -1126,7 +1178,9 @@
       <c r="C38" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>4</v>
       </c>
@@ -1272,6 +1326,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -1286,6 +1344,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1355,7 +1417,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -1377,7 +1441,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -1399,7 +1465,9 @@
       <c r="C18" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -1421,7 +1489,9 @@
       <c r="C19" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>6</v>
       </c>
@@ -1443,7 +1513,9 @@
       <c r="C20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>6</v>
       </c>
@@ -1465,7 +1537,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>7</v>
       </c>
@@ -1487,7 +1561,9 @@
       <c r="C22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -1509,7 +1585,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -1531,7 +1609,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -1553,7 +1633,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>5</v>
       </c>
@@ -1575,7 +1657,9 @@
       <c r="C26" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>5</v>
       </c>
@@ -1597,7 +1681,9 @@
       <c r="C27" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>5</v>
       </c>
@@ -1619,7 +1705,9 @@
       <c r="C28" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>8</v>
       </c>
@@ -1641,7 +1729,9 @@
       <c r="C29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>9</v>
       </c>
@@ -1663,7 +1753,9 @@
       <c r="C30" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>7</v>
       </c>
@@ -1685,7 +1777,9 @@
       <c r="C31" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>6</v>
       </c>
@@ -1707,7 +1801,9 @@
       <c r="C32" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>6</v>
       </c>
@@ -1729,7 +1825,9 @@
       <c r="C33" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>6</v>
       </c>
@@ -1751,7 +1849,9 @@
       <c r="C34" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>9</v>
       </c>
@@ -1773,7 +1873,9 @@
       <c r="C35" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>7</v>
       </c>
@@ -1795,7 +1897,9 @@
       <c r="C36" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>6</v>
       </c>
@@ -1817,7 +1921,9 @@
       <c r="C37" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>6</v>
       </c>
@@ -1839,7 +1945,9 @@
       <c r="C38" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>5</v>
       </c>
@@ -1985,6 +2093,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2000,6 +2112,10 @@
 Classroom cum workshop – 1500 sft (140 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2069,7 +2185,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -2091,7 +2209,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -2113,7 +2233,9 @@
       <c r="C18" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>8</v>
       </c>
@@ -2135,7 +2257,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>5</v>
       </c>
@@ -2157,7 +2281,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>9</v>
       </c>
@@ -2179,7 +2305,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>6</v>
       </c>
@@ -2201,7 +2329,9 @@
       <c r="C22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -2223,7 +2353,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>9</v>
       </c>
@@ -2245,7 +2377,9 @@
       <c r="C24" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>8</v>
       </c>
@@ -2267,7 +2401,9 @@
       <c r="C25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>9</v>
       </c>
@@ -2289,7 +2425,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>8</v>
       </c>
@@ -2435,6 +2573,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2450,6 +2592,10 @@
 Classroom cum workshop – 1000 sft (93 sqm) Space for Plumbing booth not included</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2519,7 +2665,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -2541,7 +2689,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -2563,7 +2713,9 @@
       <c r="C18" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -2585,7 +2737,9 @@
       <c r="C19" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>7</v>
       </c>
@@ -2607,7 +2761,9 @@
       <c r="C20" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>

--- a/lab-standards/REHAB-lab-standard.xlsx
+++ b/lab-standards/REHAB-lab-standard.xlsx
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F18" s="9">
         <f>IFERROR(MIN(C18,D18)*E18/C18,0)</f>
@@ -822,7 +822,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F23" s="9">
         <f>IFERROR(MIN(C23,D23)*E23/C23,0)</f>
@@ -870,7 +870,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F25" s="9">
         <f>IFERROR(MIN(C25,D25)*E25/C25,0)</f>
@@ -918,7 +918,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F27" s="9">
         <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F28" s="9">
         <f>IFERROR(MIN(C28,D28)*E28/C28,0)</f>
@@ -1014,7 +1014,7 @@
         <v>0</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F31" s="9">
         <f>IFERROR(MIN(C31,D31)*E31/C31,0)</f>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F32" s="9">
         <f>IFERROR(MIN(C32,D32)*E32/C32,0)</f>
@@ -1134,7 +1134,7 @@
         <v>0</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F36" s="9">
         <f>IFERROR(MIN(C36,D36)*E36/C36,0)</f>
@@ -1589,7 +1589,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F23" s="9">
         <f>IFERROR(MIN(C23,D23)*E23/C23,0)</f>
@@ -1685,7 +1685,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F27" s="9">
         <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
@@ -1733,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F29" s="9">
         <f>IFERROR(MIN(C29,D29)*E29/C29,0)</f>
@@ -1757,7 +1757,7 @@
         <v>0</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F30" s="9">
         <f>IFERROR(MIN(C30,D30)*E30/C30,0)</f>
@@ -1805,7 +1805,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F32" s="9">
         <f>IFERROR(MIN(C32,D32)*E32/C32,0)</f>
@@ -1853,7 +1853,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F34" s="9">
         <f>IFERROR(MIN(C34,D34)*E34/C34,0)</f>
@@ -1877,7 +1877,7 @@
         <v>0</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F35" s="9">
         <f>IFERROR(MIN(C35,D35)*E35/C35,0)</f>
@@ -1901,7 +1901,7 @@
         <v>0</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F36" s="9">
         <f>IFERROR(MIN(C36,D36)*E36/C36,0)</f>
@@ -1925,7 +1925,7 @@
         <v>0</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F37" s="9">
         <f>IFERROR(MIN(C37,D37)*E37/C37,0)</f>
@@ -2261,7 +2261,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F19" s="9">
         <f>IFERROR(MIN(C19,D19)*E19/C19,0)</f>
@@ -2333,7 +2333,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -2405,7 +2405,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F25" s="9">
         <f>IFERROR(MIN(C25,D25)*E25/C25,0)</f>
@@ -2429,7 +2429,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F26" s="9">
         <f>IFERROR(MIN(C26,D26)*E26/C26,0)</f>
